--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487756_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487756_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5459</v>
+        <v>2.6877</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9582</v>
+        <v>1.3181</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5876</v>
+        <v>1.3696</v>
       </c>
       <c r="G2" t="n">
         <v>1.6486</v>
@@ -610,13 +610,13 @@
         <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4973</v>
+        <v>-0.3609</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4867</v>
+        <v>-0.1534</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0106</v>
+        <v>-0.2075</v>
       </c>
       <c r="V2" t="n">
         <v>1.788</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7138</v>
+        <v>2.6245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9224</v>
+        <v>0.1476</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7914</v>
+        <v>2.4769</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7008</v>
+        <v>0.2973</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3847</v>
+        <v>-1.3388</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0855</v>
+        <v>1.6361</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6481</v>
+        <v>1.1111</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2678</v>
+        <v>-0.8197</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3803</v>
+        <v>1.9309</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9473</v>
+        <v>-0.8138</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6525</v>
+        <v>-0.5191</v>
       </c>
       <c r="O3" t="n">
         <v>-0.2948</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7164</v>
+        <v>2.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2189</v>
+        <v>-0.1489</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2445</v>
+        <v>-0.5291</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0255</v>
+        <v>0.3802</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0478</v>
+        <v>1.506</v>
       </c>
       <c r="W3" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.0478</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.118</v>
+        <v>2.5291</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4134</v>
+        <v>2.6037</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5314</v>
+        <v>-0.0745</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2973</v>
+        <v>1.0215</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3388</v>
+        <v>1.7573</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6361</v>
+        <v>-0.7358</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1111</v>
+        <v>2.4644</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8197</v>
+        <v>2.3604</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9309</v>
+        <v>0.104</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8138</v>
+        <v>-1.4429</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5191</v>
+        <v>-0.6031</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2948</v>
+        <v>-0.8398</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9702</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9105</v>
+        <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6554</v>
+        <v>-0.6401</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0902</v>
+        <v>-0.6503</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4348</v>
+        <v>0.0101</v>
       </c>
       <c r="V4" t="n">
-        <v>1.506</v>
+        <v>2.7298</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>2.7298</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8106</v>
+        <v>2.1371</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1032</v>
+        <v>0.1822</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2926</v>
+        <v>1.9549</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0215</v>
+        <v>0.7008</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7573</v>
+        <v>-0.3847</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7358</v>
+        <v>1.0855</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4644</v>
+        <v>1.6481</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3604</v>
+        <v>0.2678</v>
       </c>
       <c r="L5" t="n">
-        <v>0.104</v>
+        <v>1.3803</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4429</v>
+        <v>-0.9473</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6031</v>
+        <v>-0.6525</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8398</v>
+        <v>-0.2948</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3582</v>
+        <v>2.7164</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3587</v>
+        <v>-0.3578</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1508</v>
+        <v>-0.4958</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2079</v>
+        <v>0.138</v>
       </c>
       <c r="V5" t="n">
-        <v>2.7298</v>
+        <v>0.0478</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7298</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.589</v>
+        <v>1.5951</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3504</v>
+        <v>-0.2898</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9394</v>
+        <v>1.8849</v>
       </c>
       <c r="G6" t="n">
         <v>1.0632</v>
@@ -922,13 +922,13 @@
         <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1339</v>
+        <v>-0.1278</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1211</v>
+        <v>-0.0606</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0128</v>
+        <v>-0.0673</v>
       </c>
       <c r="V6" t="n">
         <v>0.6597</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9623</v>
+        <v>0.7047</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4166</v>
+        <v>-1.4562</v>
       </c>
       <c r="F7" t="n">
-        <v>2.379</v>
+        <v>2.1609</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1095</v>
@@ -1000,13 +1000,13 @@
         <v>2.7164</v>
       </c>
       <c r="S7" t="n">
-        <v>0.024</v>
+        <v>-0.2336</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.544</v>
+        <v>-0.5835</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="V7" t="n">
         <v>1.2716</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0979</v>
+        <v>-0.261</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4243</v>
+        <v>0.2764</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6737</v>
+        <v>-0.5374</v>
       </c>
       <c r="G8" t="n">
         <v>0.6427</v>
@@ -1078,13 +1078,13 @@
         <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3526</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3325</v>
+        <v>-0.6318</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0202</v>
+        <v>0.1161</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9556</v>
+        <v>-3.0106</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6189</v>
+        <v>-0.9192</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3367</v>
+        <v>-2.0914</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1538</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6362</v>
+        <v>-0.6912</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0011</v>
+        <v>-0.2992</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6373</v>
+        <v>-0.392</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5537</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.943</v>
+        <v>-4.2433</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6914</v>
+        <v>-1.9917</v>
       </c>
       <c r="F10" t="n">
         <v>-2.2515</v>
@@ -1234,10 +1234,10 @@
         <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6427</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1806</v>
+        <v>-0.4809</v>
       </c>
       <c r="U10" t="n">
         <v>-0.4621</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8248</v>
+        <v>-5.5423</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8229</v>
+        <v>-3.3224</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0019</v>
+        <v>-2.2199</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8365</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5406</v>
+        <v>-1.2581</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3325</v>
+        <v>-0.832</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2081</v>
+        <v>-0.4262</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2239</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0817</v>
+        <v>-0.778999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7541</v>
+        <v>-3.4513</v>
       </c>
       <c r="F12" t="n">
-        <v>2.672400000000001</v>
+        <v>2.672499999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0857</v>
@@ -1369,7 +1369,7 @@
         <v>3.855900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>4.866399999999999</v>
+        <v>4.8664</v>
       </c>
       <c r="M12" t="n">
         <v>-9.8078</v>
@@ -1390,13 +1390,13 @@
         <v>17.4629</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.5799</v>
+        <v>-5.276999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.0194</v>
+        <v>-4.716600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5605</v>
+        <v>-0.5607000000000002</v>
       </c>
       <c r="V12" t="n">
         <v>4.6134</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.174</v>
+        <v>4.5476</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0588</v>
+        <v>4.1598</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1152</v>
+        <v>0.3878</v>
       </c>
       <c r="G13" t="n">
         <v>3.951</v>
@@ -1468,13 +1468,13 @@
         <v>2.7164</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8367</v>
+        <v>0.5369</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3201</v>
+        <v>-0.219</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4834</v>
+        <v>0.756</v>
       </c>
       <c r="V13" t="n">
         <v>1.2239</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3797</v>
+        <v>2.2712</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2133</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.593</v>
+        <v>2.1842</v>
       </c>
       <c r="G14" t="n">
         <v>2.3756</v>
@@ -1546,13 +1546,13 @@
         <v>3.1045</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3638</v>
+        <v>1.2553</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0145</v>
+        <v>0.3148</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3493</v>
+        <v>0.9405</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5537</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8133</v>
+        <v>2.2677</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5462</v>
+        <v>1.6463</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2671</v>
+        <v>0.6214</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3331</v>
@@ -1624,13 +1624,13 @@
         <v>2.3284</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1285</v>
+        <v>0.5829</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1233</v>
+        <v>0.2234</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0052</v>
+        <v>0.3595</v>
       </c>
       <c r="V15" t="n">
         <v>0.6597</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>P. FUENTE DIEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4771</v>
+        <v>1.4493</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07530000000000001</v>
+        <v>1.2838</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5523</v>
+        <v>0.1655</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.7331</v>
+        <v>1.7153</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5659999999999999</v>
+        <v>1.0892</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.1671</v>
+        <v>0.6262</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.9679</v>
+        <v>1.3321</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1689</v>
+        <v>0.7003</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.799</v>
+        <v>0.6318</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7652</v>
+        <v>0.3833</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3971</v>
+        <v>0.3889</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3681</v>
+        <v>-0.0056</v>
       </c>
       <c r="P16" t="n">
-        <v>0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1344</v>
+        <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4519</v>
+        <v>0.1817</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9867</v>
+        <v>-0.0482</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4653</v>
+        <v>0.2299</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5642</v>
+        <v>-1.2239</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3359</v>
+        <v>1.2641</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3249</v>
+        <v>0.1756</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6608</v>
+        <v>1.0885</v>
       </c>
       <c r="G17" t="n">
         <v>3.4074</v>
@@ -1780,13 +1780,13 @@
         <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4047</v>
+        <v>0.3328</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0296</v>
+        <v>-0.5291</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4343</v>
+        <v>0.862</v>
       </c>
       <c r="V17" t="n">
         <v>-1.506</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. FUENTE DIEZ</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2313</v>
+        <v>-0.6429</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2838</v>
+        <v>-1.9772</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0526</v>
+        <v>1.3343</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7153</v>
+        <v>-3.7331</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0892</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6262</v>
+        <v>-3.1671</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3321</v>
+        <v>-1.9679</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7003</v>
+        <v>-0.1689</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6318</v>
+        <v>-1.799</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3833</v>
+        <v>-1.7652</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3889</v>
+        <v>-0.3971</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0056</v>
+        <v>-1.3681</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7761</v>
+        <v>2.1344</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0363</v>
+        <v>2.332</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0482</v>
+        <v>1.0848</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0119</v>
+        <v>1.2472</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2239</v>
+        <v>0.5642</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1807</v>
+        <v>-1.0479</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4356</v>
+        <v>-1.9349</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2549</v>
+        <v>0.8871</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.9484</v>
+        <v>0.5702</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7942</v>
+        <v>-0.2595</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.1542</v>
+        <v>0.8297</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.6616</v>
+        <v>0.8159</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4696</v>
+        <v>-0.5643</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.192</v>
+        <v>1.3803</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2867</v>
+        <v>-0.2458</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3246</v>
+        <v>0.3048</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9621</v>
+        <v>-0.5506</v>
       </c>
       <c r="P19" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.7761</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9702</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.7463</v>
-      </c>
       <c r="S19" t="n">
-        <v>1.4378</v>
+        <v>0.2058</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9724</v>
+        <v>-0.1509</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4655</v>
+        <v>0.3567</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5537</v>
+        <v>-0.6597</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2239</v>
+        <v>-0.6597</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3026</v>
+        <v>-1.5449</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1351</v>
+        <v>-2.9361</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8325</v>
+        <v>1.3912</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5702</v>
+        <v>-4.9484</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2595</v>
+        <v>-0.7942</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8297</v>
+        <v>-4.1542</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8159</v>
+        <v>-3.6616</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5643</v>
+        <v>-0.4696</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3803</v>
+        <v>-3.192</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2458</v>
+        <v>-1.2867</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3048</v>
+        <v>-0.3246</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5506</v>
+        <v>-0.9621</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0489</v>
+        <v>1.0736</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3511</v>
+        <v>0.4719</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3022</v>
+        <v>0.6018</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6597</v>
+        <v>1.5537</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6597</v>
+        <v>1.2239</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="21">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.8228</v>
+        <v>-5.459</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1953</v>
+        <v>-2.9951</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6274</v>
+        <v>-2.4639</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4349</v>
@@ -2170,13 +2170,13 @@
         <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9699</v>
+        <v>-0.6062</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3643</v>
+        <v>-0.2007</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4477</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.081700000000001</v>
+        <v>1.0817</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6724</v>
+        <v>-2.672500000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>3.753999999999998</v>
+        <v>3.7543</v>
       </c>
       <c r="G23" t="n">
         <v>1.085599999999999</v>
@@ -2218,13 +2218,13 @@
         <v>3.6993</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6136</v>
+        <v>-2.613600000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>9.807600000000001</v>
+        <v>9.807599999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>7.5551</v>
+        <v>7.555100000000001</v>
       </c>
       <c r="L23" t="n">
         <v>2.2528</v>
@@ -2233,7 +2233,7 @@
         <v>-8.722100000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.855799999999999</v>
+        <v>-3.8558</v>
       </c>
       <c r="O23" t="n">
         <v>-4.8662</v>
@@ -2248,13 +2248,13 @@
         <v>16.4927</v>
       </c>
       <c r="S23" t="n">
-        <v>5.5797</v>
+        <v>5.579599999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5604999999999997</v>
+        <v>0.5605</v>
       </c>
       <c r="U23" t="n">
-        <v>5.0193</v>
+        <v>5.0194</v>
       </c>
       <c r="V23" t="n">
         <v>-4.6134</v>
